--- a/data/trans_orig/P44A$endoscopia-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P44A$endoscopia-Habitat-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tipo de prueba realizada para detectar cáncer de colon-recto (multirrespuesta) en 2012</t>
+          <t>Población según el tipo de prueba realizada para detectar cáncer de colon-recto (multirrespuesta) en 2012 (tasa de respuesta: 96,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3971</t>
+          <t>4106</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11641</t>
+          <t>11855</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>27,01%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>76,58%</t>
+          <t>77,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6129</t>
+          <t>6221</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13277</t>
+          <t>13250</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>40,32%</t>
+          <t>40,93%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>87,35%</t>
+          <t>87,17%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12761</t>
+          <t>12112</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>22764</t>
+          <t>23213</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>41,98%</t>
+          <t>39,84%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>74,88%</t>
+          <t>76,36%</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6403</t>
+          <t>5248</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>42,12%</t>
+          <t>34,53%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>935</t>
+          <t>928</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6982</t>
+          <t>7168</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>45,94%</t>
+          <t>47,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1110</t>
+          <t>1916</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>10132</t>
+          <t>10387</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,33%</t>
+          <t>34,17%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2913</t>
+          <t>2968</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10254</t>
+          <t>10428</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>67,46%</t>
+          <t>68,6%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1010</t>
+          <t>1009</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7374</t>
+          <t>7495</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>48,51%</t>
+          <t>49,31%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5030</t>
+          <t>4975</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>14636</t>
+          <t>15306</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>48,14%</t>
+          <t>50,35%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1944</t>
+          <t>1092</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8438</t>
+          <t>8338</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>55,51%</t>
+          <t>54,85%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>923</t>
+          <t>933</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7052</t>
+          <t>7077</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>46,39%</t>
+          <t>46,56%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3070</t>
+          <t>3032</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12196</t>
+          <t>13205</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>40,12%</t>
+          <t>43,44%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>10659</t>
+          <t>10637</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>21999</t>
+          <t>21295</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>40,41%</t>
+          <t>40,32%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>83,39%</t>
+          <t>80,72%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>18541</t>
+          <t>17443</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>30070</t>
+          <t>29817</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>50,98%</t>
+          <t>47,96%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>82,68%</t>
+          <t>81,99%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>32742</t>
+          <t>33226</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>48188</t>
+          <t>48902</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>52,18%</t>
+          <t>52,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>76,79%</t>
+          <t>77,93%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>890</t>
+          <t>930</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8153</t>
+          <t>8192</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>31,06%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1341,7 +1341,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5162</t>
+          <t>4947</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1356,7 +1356,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1021</t>
+          <t>1009</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>9146</t>
+          <t>8723</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>13,9%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6335</t>
+          <t>6485</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17823</t>
+          <t>18337</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>67,56%</t>
+          <t>69,51%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7365</t>
+          <t>7413</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19002</t>
+          <t>18897</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>52,25%</t>
+          <t>51,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>16961</t>
+          <t>17190</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>32854</t>
+          <t>32835</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>52,36%</t>
+          <t>52,33%</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6925</t>
+          <t>6791</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7590</t>
+          <t>7825</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>20861</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>21,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>54,99%</t>
+          <t>57,36%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>9655</t>
+          <t>9462</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>23469</t>
+          <t>23250</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>37,4%</t>
+          <t>37,05%</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>12139</t>
+          <t>11531</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>23067</t>
+          <t>22837</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>46,06%</t>
+          <t>43,75%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>87,52%</t>
+          <t>86,65%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>10449</t>
+          <t>11005</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>21173</t>
+          <t>21677</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>39,55%</t>
+          <t>41,66%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>80,14%</t>
+          <t>82,05%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>25672</t>
+          <t>25902</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>40854</t>
+          <t>40865</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>48,64%</t>
+          <t>49,08%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>77,41%</t>
+          <t>77,43%</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>996</t>
+          <t>948</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7792</t>
+          <t>7533</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>28,58%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>970</t>
+          <t>958</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7531</t>
+          <t>7835</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>29,65%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2137</t>
+          <t>3031</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11715</t>
+          <t>13969</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>26,47%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4263</t>
+          <t>4783</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>14954</t>
+          <t>15299</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>56,74%</t>
+          <t>58,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>4290</t>
+          <t>4114</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>14157</t>
+          <t>14405</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>53,58%</t>
+          <t>54,52%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>11863</t>
+          <t>11988</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>25807</t>
+          <t>25933</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>48,9%</t>
+          <t>49,14%</t>
         </is>
       </c>
     </row>
@@ -1983,12 +1983,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1144</t>
+          <t>1170</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>11336</t>
+          <t>12374</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1998,12 +1998,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>43,01%</t>
+          <t>46,95%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4326</t>
+          <t>4248</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>14244</t>
+          <t>14199</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2033,12 +2033,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>53,91%</t>
+          <t>53,74%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2053,12 +2053,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7744</t>
+          <t>7754</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>22677</t>
+          <t>22495</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2068,12 +2068,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>42,97%</t>
+          <t>42,63%</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>18073</t>
+          <t>17600</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>31513</t>
+          <t>30975</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>43,62%</t>
+          <t>42,48%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>76,06%</t>
+          <t>74,76%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9328</t>
+          <t>9404</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>20840</t>
+          <t>20679</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>32,21%</t>
+          <t>32,47%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>71,96%</t>
+          <t>71,4%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>30874</t>
+          <t>30753</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>48500</t>
+          <t>48550</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>43,86%</t>
+          <t>43,69%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>68,9%</t>
+          <t>68,97%</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5751</t>
+          <t>6128</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17893</t>
+          <t>18673</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>43,19%</t>
+          <t>45,07%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7397</t>
+          <t>8367</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>28,89%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>7235</t>
+          <t>7104</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>21477</t>
+          <t>20600</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>30,51%</t>
+          <t>29,26%</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>7813</t>
+          <t>7914</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>20762</t>
+          <t>20420</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>50,11%</t>
+          <t>49,29%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4429</t>
+          <t>4377</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>15465</t>
+          <t>15064</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>53,4%</t>
+          <t>52,01%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>14985</t>
+          <t>14509</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>31902</t>
+          <t>31099</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>45,32%</t>
+          <t>44,18%</t>
         </is>
       </c>
     </row>
@@ -2439,12 +2439,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2834</t>
+          <t>2097</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12926</t>
+          <t>11596</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2454,12 +2454,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>27,99%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2474,12 +2474,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6881</t>
+          <t>5910</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>17890</t>
+          <t>17285</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2489,12 +2489,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>61,77%</t>
+          <t>59,68%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2509,12 +2509,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>10705</t>
+          <t>11283</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>26729</t>
+          <t>26756</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2524,12 +2524,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>38,01%</t>
         </is>
       </c>
     </row>
@@ -2556,12 +2556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>56432</t>
+          <t>57249</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>78039</t>
+          <t>77847</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>51,6%</t>
+          <t>52,35%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>71,36%</t>
+          <t>71,18%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2591,12 +2591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>55368</t>
+          <t>55232</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>76114</t>
+          <t>76516</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2606,12 +2606,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>51,77%</t>
+          <t>51,64%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>71,17%</t>
+          <t>71,54%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>118116</t>
+          <t>117916</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>149759</t>
+          <t>147087</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>54,6%</t>
+          <t>54,51%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>69,23%</t>
+          <t>68,0%</t>
         </is>
       </c>
     </row>
@@ -2669,12 +2669,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>12122</t>
+          <t>12226</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>30912</t>
+          <t>29752</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2684,12 +2684,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>27,2%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>4504</t>
+          <t>4125</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>16699</t>
+          <t>16680</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2719,12 +2719,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>19953</t>
+          <t>19817</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>41268</t>
+          <t>40649</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>18,79%</t>
         </is>
       </c>
     </row>
@@ -2782,12 +2782,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>30607</t>
+          <t>30546</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>52072</t>
+          <t>53643</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2797,82 +2797,82 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
+          <t>27,93%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>49,05%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>33771</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>24440</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>45004</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>31,58%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>22,85%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>42,08%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>74842</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>60545</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>90964</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>34,6%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
           <t>27,99%</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>47,61%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>33771</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>25357</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>44873</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>31,58%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>23,71%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>41,96%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>74842</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>61085</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>90565</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>34,6%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>28,24%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>41,87%</t>
+          <t>42,05%</t>
         </is>
       </c>
     </row>
@@ -2895,12 +2895,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>10251</t>
+          <t>10773</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>27241</t>
+          <t>27710</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2910,12 +2910,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>26798</t>
+          <t>28103</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>47477</t>
+          <t>50006</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2945,12 +2945,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>26,28%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>44,39%</t>
+          <t>46,76%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>41016</t>
+          <t>41755</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>69024</t>
+          <t>70122</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2980,12 +2980,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>32,42%</t>
         </is>
       </c>
     </row>
@@ -3049,7 +3049,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tipo de prueba realizada para detectar cáncer de colon-recto (multirrespuesta) en 2016</t>
+          <t>Población según el tipo de prueba realizada para detectar cáncer de colon-recto (multirrespuesta) en 2016 (tasa de respuesta: 96,56%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7427</t>
+          <t>7393</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18970</t>
+          <t>18947</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>61,41%</t>
+          <t>61,34%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8606</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18641</t>
+          <t>18702</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>33,67%</t>
+          <t>31,48%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>72,92%</t>
+          <t>73,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>18689</t>
+          <t>18653</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>34466</t>
+          <t>34258</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>33,11%</t>
+          <t>33,04%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>61,05%</t>
+          <t>60,68%</t>
         </is>
       </c>
     </row>
@@ -3362,7 +3362,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8599</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1003</t>
+          <t>1018</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8439</t>
+          <t>8272</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3407,12 +3407,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>32,36%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>1656</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>11709</t>
+          <t>11708</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3442,7 +3442,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -3470,12 +3470,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3846</t>
+          <t>4134</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14480</t>
+          <t>14742</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3485,12 +3485,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>46,88%</t>
+          <t>47,73%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3505,12 +3505,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1895</t>
+          <t>2052</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10405</t>
+          <t>10475</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3520,12 +3520,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>40,7%</t>
+          <t>40,98%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>7757</t>
+          <t>7843</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>21857</t>
+          <t>21813</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>38,72%</t>
+          <t>38,64%</t>
         </is>
       </c>
     </row>
@@ -3583,12 +3583,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5940</t>
+          <t>6212</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16893</t>
+          <t>17892</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3598,12 +3598,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>54,69%</t>
+          <t>57,92%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3618,12 +3618,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5355</t>
+          <t>5036</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16007</t>
+          <t>15518</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3633,12 +3633,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>62,62%</t>
+          <t>60,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3653,12 +3653,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13797</t>
+          <t>14189</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>29114</t>
+          <t>29426</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3668,12 +3668,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>51,57%</t>
+          <t>52,13%</t>
         </is>
       </c>
     </row>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>17022</t>
+          <t>17465</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>28982</t>
+          <t>29173</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>43,09%</t>
+          <t>44,21%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>73,36%</t>
+          <t>73,85%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>10237</t>
+          <t>10486</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>22848</t>
+          <t>23152</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>31,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>67,85%</t>
+          <t>68,75%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>30851</t>
+          <t>30889</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>48096</t>
+          <t>48798</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3785,12 +3785,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>42,16%</t>
+          <t>42,21%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>65,72%</t>
+          <t>66,68%</t>
         </is>
       </c>
     </row>
@@ -3813,12 +3813,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2730</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11946</t>
+          <t>11858</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3828,12 +3828,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>30,02%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3853,7 +3853,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6319</t>
+          <t>6700</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3868,7 +3868,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>3930</t>
+          <t>3752</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>14835</t>
+          <t>14392</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>19,67%</t>
         </is>
       </c>
     </row>
@@ -3926,12 +3926,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11553</t>
+          <t>11601</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23431</t>
+          <t>23557</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3941,12 +3941,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>29,24%</t>
+          <t>29,37%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>59,31%</t>
+          <t>59,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7273</t>
+          <t>6887</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19775</t>
+          <t>19065</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3976,12 +3976,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>58,72%</t>
+          <t>56,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>22123</t>
+          <t>22349</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>40368</t>
+          <t>39872</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4011,12 +4011,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>30,23%</t>
+          <t>30,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>55,16%</t>
+          <t>54,49%</t>
         </is>
       </c>
     </row>
@@ -4039,12 +4039,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>847</t>
+          <t>811</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8170</t>
+          <t>7237</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4054,12 +4054,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4074,12 +4074,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2114</t>
+          <t>2085</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11859</t>
+          <t>12120</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>35,22%</t>
+          <t>35,99%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4109,12 +4109,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4194</t>
+          <t>4085</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>15691</t>
+          <t>15754</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>21,53%</t>
         </is>
       </c>
     </row>
@@ -4156,12 +4156,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>12458</t>
+          <t>12217</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>23754</t>
+          <t>23262</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>40,46%</t>
+          <t>39,68%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>75,55%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5803</t>
+          <t>6471</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>15716</t>
+          <t>15605</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>31,87%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>77,41%</t>
+          <t>76,87%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>22060</t>
+          <t>22057</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>36110</t>
+          <t>36240</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4241,12 +4241,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>43,18%</t>
+          <t>43,17%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>70,68%</t>
+          <t>70,93%</t>
         </is>
       </c>
     </row>
@@ -4269,12 +4269,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>849</t>
+          <t>862</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7253</t>
+          <t>7735</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4309,7 +4309,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5562</t>
+          <t>5628</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4324,7 +4324,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>27,72%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1064</t>
+          <t>1098</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9431</t>
+          <t>9170</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>17,95%</t>
         </is>
       </c>
     </row>
@@ -4382,12 +4382,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2973</t>
+          <t>2914</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>12510</t>
+          <t>12747</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>40,63%</t>
+          <t>41,4%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2369</t>
+          <t>2282</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>11011</t>
+          <t>11213</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>54,24%</t>
+          <t>55,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>7590</t>
+          <t>7385</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>19929</t>
+          <t>20124</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>39,01%</t>
+          <t>39,39%</t>
         </is>
       </c>
     </row>
@@ -4495,12 +4495,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>3201</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>13420</t>
+          <t>13162</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4510,12 +4510,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>43,59%</t>
+          <t>42,75%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -4530,12 +4530,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1008</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>7930</t>
+          <t>7842</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>39,06%</t>
+          <t>38,63%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -4565,12 +4565,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>5630</t>
+          <t>5244</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>17612</t>
+          <t>17726</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>34,47%</t>
+          <t>34,69%</t>
         </is>
       </c>
     </row>
@@ -4612,12 +4612,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>20435</t>
+          <t>20443</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>35242</t>
+          <t>36255</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>34,93%</t>
+          <t>34,94%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>60,24%</t>
+          <t>61,97%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4647,12 +4647,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>16850</t>
+          <t>17534</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>29293</t>
+          <t>29856</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>46,05%</t>
+          <t>47,93%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>80,06%</t>
+          <t>81,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4682,12 +4682,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>42355</t>
+          <t>41582</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>62285</t>
+          <t>62377</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>44,54%</t>
+          <t>43,73%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>65,5%</t>
+          <t>65,6%</t>
         </is>
       </c>
     </row>
@@ -4725,12 +4725,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2431</t>
+          <t>2575</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13473</t>
+          <t>13155</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4760,12 +4760,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>955</t>
+          <t>961</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8330</t>
+          <t>8094</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4795,12 +4795,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4922</t>
+          <t>4985</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>16767</t>
+          <t>17343</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>18,24%</t>
         </is>
       </c>
     </row>
@@ -4838,12 +4838,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>17831</t>
+          <t>18007</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>33705</t>
+          <t>32390</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4853,12 +4853,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>30,78%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>57,61%</t>
+          <t>55,36%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4873,12 +4873,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>8845</t>
+          <t>8793</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>21261</t>
+          <t>21655</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>58,11%</t>
+          <t>59,19%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4908,12 +4908,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>30969</t>
+          <t>30642</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>50960</t>
+          <t>49897</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>32,57%</t>
+          <t>32,22%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>53,59%</t>
+          <t>52,47%</t>
         </is>
       </c>
     </row>
@@ -4951,12 +4951,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9666</t>
+          <t>9591</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>23222</t>
+          <t>24213</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4966,12 +4966,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>39,69%</t>
+          <t>41,39%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5423</t>
+          <t>5289</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>18291</t>
+          <t>17783</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5001,12 +5001,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>49,99%</t>
+          <t>48,6%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5021,12 +5021,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>17334</t>
+          <t>17918</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>36366</t>
+          <t>36937</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>38,24%</t>
+          <t>38,84%</t>
         </is>
       </c>
     </row>
@@ -5068,12 +5068,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>70282</t>
+          <t>69928</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>95764</t>
+          <t>95964</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5083,82 +5083,82 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>44,01%</t>
+          <t>43,79%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
+          <t>60,1%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>65140</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>52283</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>76630</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>56,09%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>45,02%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>65,99%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>147844</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>131253</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>165398</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>53,6%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>47,59%</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
           <t>59,97%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>65140</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>53248</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>76196</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>56,09%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>45,85%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>65,62%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>136</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>147844</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>130232</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>164680</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>53,6%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>47,22%</t>
-        </is>
-      </c>
-      <c r="W20" s="2" t="inlineStr">
-        <is>
-          <t>59,71%</t>
         </is>
       </c>
     </row>
@@ -5181,12 +5181,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>10801</t>
+          <t>10482</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>26726</t>
+          <t>26977</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5196,12 +5196,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5216,12 +5216,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>4410</t>
+          <t>4200</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>16270</t>
+          <t>15993</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5251,12 +5251,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>17810</t>
+          <t>17675</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>37903</t>
+          <t>38486</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,95%</t>
         </is>
       </c>
     </row>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>46469</t>
+          <t>47067</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>70793</t>
+          <t>71353</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5309,12 +5309,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>29,47%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>44,33%</t>
+          <t>44,68%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5329,12 +5329,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>29533</t>
+          <t>28939</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>51612</t>
+          <t>51378</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5344,12 +5344,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>44,45%</t>
+          <t>44,24%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5364,12 +5364,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>82559</t>
+          <t>80188</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>115787</t>
+          <t>113112</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5379,12 +5379,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>29,93%</t>
+          <t>29,07%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>41,98%</t>
+          <t>41,01%</t>
         </is>
       </c>
     </row>
@@ -5407,12 +5407,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>26601</t>
+          <t>26384</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>47997</t>
+          <t>47921</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5422,12 +5422,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>30,01%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>20859</t>
+          <t>21031</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>40485</t>
+          <t>40709</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5457,12 +5457,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>34,86%</t>
+          <t>35,06%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>54103</t>
+          <t>52593</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>83751</t>
+          <t>82205</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5492,12 +5492,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>29,8%</t>
         </is>
       </c>
     </row>
@@ -5561,7 +5561,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tipo de prueba realizada para detectar cáncer de colon-recto (multirrespuesta) en 2023</t>
+          <t>Población según el tipo de prueba realizada para detectar cáncer de colon-recto (multirrespuesta) en 2023 (tasa de respuesta: 99,5%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5756,12 +5756,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>32103</t>
+          <t>32324</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>48405</t>
+          <t>48801</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5771,12 +5771,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>34,94%</t>
+          <t>35,18%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>52,68%</t>
+          <t>53,11%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5791,12 +5791,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>33306</t>
+          <t>33188</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>46489</t>
+          <t>46255</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>34,04%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>47,68%</t>
+          <t>47,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5826,12 +5826,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>69795</t>
+          <t>68782</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>91600</t>
+          <t>89735</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>36,85%</t>
+          <t>36,32%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>48,37%</t>
+          <t>47,38%</t>
         </is>
       </c>
     </row>
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>51878</t>
+          <t>51753</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>67526</t>
+          <t>66957</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5884,12 +5884,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>56,46%</t>
+          <t>56,32%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>73,48%</t>
+          <t>72,87%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5904,12 +5904,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>51395</t>
+          <t>51534</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>64697</t>
+          <t>64418</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>52,71%</t>
+          <t>52,86%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>66,36%</t>
+          <t>66,07%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5939,12 +5939,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>107894</t>
+          <t>107939</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>127943</t>
+          <t>128460</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>56,97%</t>
+          <t>56,99%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>67,55%</t>
+          <t>67,83%</t>
         </is>
       </c>
     </row>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2341</t>
+          <t>2319</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10737</t>
+          <t>10715</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5997,12 +5997,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6017,12 +6017,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6154</t>
+          <t>5808</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>14375</t>
+          <t>14130</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6032,12 +6032,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6052,12 +6052,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>10034</t>
+          <t>9960</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>21618</t>
+          <t>21830</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6067,12 +6067,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,53%</t>
         </is>
       </c>
     </row>
@@ -6100,7 +6100,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3225</t>
+          <t>3043</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6115,7 +6115,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6135,7 +6135,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1894</t>
+          <t>2075</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6170,7 +6170,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3178</t>
+          <t>3307</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6185,7 +6185,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -6212,12 +6212,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>160403</t>
+          <t>159533</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>365945</t>
+          <t>364084</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>41,45%</t>
+          <t>41,23%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6247,12 +6247,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>41389</t>
+          <t>42507</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>57222</t>
+          <t>58241</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>32,54%</t>
+          <t>33,42%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>44,99%</t>
+          <t>45,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6282,12 +6282,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>206835</t>
+          <t>208066</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>465082</t>
+          <t>457506</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>40,23%</t>
+          <t>40,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,45%</t>
+          <t>88,98%</t>
         </is>
       </c>
     </row>
@@ -6325,12 +6325,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>248100</t>
+          <t>251674</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>374530</t>
+          <t>375139</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6340,12 +6340,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>64,11%</t>
+          <t>65,04%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6360,12 +6360,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>82878</t>
+          <t>82874</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>97353</t>
+          <t>97268</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6380,7 +6380,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>76,54%</t>
+          <t>76,48%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6395,12 +6395,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>347421</t>
+          <t>345243</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>490802</t>
+          <t>486901</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6410,12 +6410,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>67,57%</t>
+          <t>67,15%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>94,7%</t>
         </is>
       </c>
     </row>
@@ -6438,12 +6438,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>44087</t>
+          <t>43272</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>355243</t>
+          <t>353332</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6453,12 +6453,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>91,8%</t>
+          <t>91,3%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10991</t>
+          <t>11379</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22303</t>
+          <t>23097</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6488,12 +6488,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6508,12 +6508,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>60766</t>
+          <t>61145</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>441052</t>
+          <t>432740</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6523,12 +6523,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>85,78%</t>
+          <t>84,16%</t>
         </is>
       </c>
     </row>
@@ -6556,7 +6556,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7893</t>
+          <t>7598</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6571,7 +6571,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6591,7 +6591,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2084</t>
+          <t>2266</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6606,7 +6606,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6626,7 +6626,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>6145</t>
+          <t>6229</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6641,7 +6641,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,21%</t>
         </is>
       </c>
     </row>
@@ -6668,12 +6668,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>33685</t>
+          <t>33704</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>51777</t>
+          <t>52191</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>31,58%</t>
+          <t>31,6%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>48,55%</t>
+          <t>48,93%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6703,12 +6703,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>19916</t>
+          <t>19851</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>31425</t>
+          <t>32231</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>27,45%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>43,46%</t>
+          <t>44,58%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6738,12 +6738,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>55881</t>
+          <t>58053</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>78412</t>
+          <t>80487</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6753,12 +6753,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>31,23%</t>
+          <t>32,44%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>43,82%</t>
+          <t>44,97%</t>
         </is>
       </c>
     </row>
@@ -6781,12 +6781,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>56705</t>
+          <t>55456</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>74434</t>
+          <t>74504</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>53,17%</t>
+          <t>52,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>69,79%</t>
+          <t>69,86%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6816,12 +6816,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>50210</t>
+          <t>49997</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>60389</t>
+          <t>60808</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>69,44%</t>
+          <t>69,15%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>83,52%</t>
+          <t>84,1%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6851,12 +6851,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>110898</t>
+          <t>110452</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>131698</t>
+          <t>131492</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6866,12 +6866,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>61,97%</t>
+          <t>61,72%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>73,59%</t>
+          <t>73,48%</t>
         </is>
       </c>
     </row>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>18330</t>
+          <t>18049</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>35713</t>
+          <t>34662</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>33,48%</t>
+          <t>32,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6929,12 +6929,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>7722</t>
+          <t>7489</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>17130</t>
+          <t>17025</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>28258</t>
+          <t>28788</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>47583</t>
+          <t>47591</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6979,7 +6979,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5038</t>
+          <t>5048</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7027,7 +7027,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -7047,7 +7047,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4480</t>
+          <t>4491</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7062,7 +7062,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -7077,12 +7077,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>595</t>
+          <t>592</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7037</t>
+          <t>7296</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7097,7 +7097,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,08%</t>
         </is>
       </c>
     </row>
@@ -7124,12 +7124,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>68903</t>
+          <t>66950</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>93244</t>
+          <t>90642</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>36,04%</t>
+          <t>35,02%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>48,77%</t>
+          <t>47,41%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>50894</t>
+          <t>50636</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>70757</t>
+          <t>69606</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>27,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>39,07%</t>
+          <t>38,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7194,12 +7194,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>124362</t>
+          <t>125489</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>155195</t>
+          <t>155358</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7209,12 +7209,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>33,4%</t>
+          <t>33,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>41,68%</t>
+          <t>41,73%</t>
         </is>
       </c>
     </row>
@@ -7237,12 +7237,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>112568</t>
+          <t>113156</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>134699</t>
+          <t>135936</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7252,12 +7252,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>58,87%</t>
+          <t>59,18%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>70,45%</t>
+          <t>71,1%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7272,12 +7272,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>123260</t>
+          <t>123944</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>142381</t>
+          <t>141895</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7287,12 +7287,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>68,05%</t>
+          <t>68,43%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>78,61%</t>
+          <t>78,34%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7307,12 +7307,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>244706</t>
+          <t>243682</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>274153</t>
+          <t>272746</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7322,12 +7322,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>65,72%</t>
+          <t>65,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>73,63%</t>
+          <t>73,26%</t>
         </is>
       </c>
     </row>
@@ -7350,12 +7350,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>14429</t>
+          <t>14820</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>30389</t>
+          <t>30572</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7365,12 +7365,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7385,12 +7385,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>10794</t>
+          <t>11601</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>22366</t>
+          <t>23136</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7420,12 +7420,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>29113</t>
+          <t>29513</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>48491</t>
+          <t>48725</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7435,12 +7435,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>13,09%</t>
         </is>
       </c>
     </row>
@@ -7463,97 +7463,97 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>1385</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>0,72%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>1080</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>0,6%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>1220</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -7580,12 +7580,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>320782</t>
+          <t>324645</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>647154</t>
+          <t>638546</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7595,12 +7595,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>41,3%</t>
+          <t>41,8%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>83,32%</t>
+          <t>82,21%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7615,12 +7615,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>158068</t>
+          <t>159143</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>188697</t>
+          <t>189444</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7630,12 +7630,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>33,06%</t>
+          <t>33,29%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>39,47%</t>
+          <t>39,62%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7650,12 +7650,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>488756</t>
+          <t>488561</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>910962</t>
+          <t>939193</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7665,12 +7665,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>38,95%</t>
+          <t>38,93%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>72,6%</t>
+          <t>74,85%</t>
         </is>
       </c>
     </row>
@@ -7693,12 +7693,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>494134</t>
+          <t>491588</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>696550</t>
+          <t>699871</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7708,12 +7708,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>63,62%</t>
+          <t>63,29%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>89,68%</t>
+          <t>90,1%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7728,12 +7728,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>323638</t>
+          <t>323663</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>353144</t>
+          <t>351987</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7743,12 +7743,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>67,69%</t>
+          <t>67,7%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>73,86%</t>
+          <t>73,62%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>837575</t>
+          <t>840970</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1075311</t>
+          <t>1087759</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7778,12 +7778,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>66,75%</t>
+          <t>67,02%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>85,69%</t>
+          <t>86,69%</t>
         </is>
       </c>
     </row>
@@ -7806,12 +7806,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>100031</t>
+          <t>96806</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>577175</t>
+          <t>574811</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>74,31%</t>
+          <t>74,0%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7841,12 +7841,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>44190</t>
+          <t>44454</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>64092</t>
+          <t>64367</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7856,12 +7856,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7876,12 +7876,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>149064</t>
+          <t>148812</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>759094</t>
+          <t>786892</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7891,12 +7891,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>60,49%</t>
+          <t>62,71%</t>
         </is>
       </c>
     </row>
@@ -7919,12 +7919,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>509</t>
+          <t>516</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>8172</t>
+          <t>8265</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7939,7 +7939,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7954,12 +7954,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>747</t>
+          <t>594</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>5927</t>
+          <t>5537</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7969,12 +7969,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7989,12 +7989,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2053</t>
+          <t>2137</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>11182</t>
+          <t>10686</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8004,12 +8004,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,85%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P44A$endoscopia-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P44A$endoscopia-Habitat-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4106</t>
+          <t>3747</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11855</t>
+          <t>11242</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>77,99%</t>
+          <t>73,95%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6221</t>
+          <t>6125</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13250</t>
+          <t>13227</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>40,93%</t>
+          <t>40,29%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>87,17%</t>
+          <t>87,02%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12112</t>
+          <t>13116</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>23213</t>
+          <t>23368</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>39,84%</t>
+          <t>43,14%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>76,36%</t>
+          <t>76,87%</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5248</t>
+          <t>6122</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>34,53%</t>
+          <t>40,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7168</t>
+          <t>7142</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>47,16%</t>
+          <t>46,98%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1916</t>
+          <t>1945</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>10387</t>
+          <t>10155</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>34,17%</t>
+          <t>33,4%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2968</t>
+          <t>2987</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10428</t>
+          <t>10170</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>68,6%</t>
+          <t>66,9%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1009</t>
+          <t>1014</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7495</t>
+          <t>7324</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>49,31%</t>
+          <t>48,19%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4975</t>
+          <t>4845</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>15306</t>
+          <t>15027</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>50,35%</t>
+          <t>49,43%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1092</t>
+          <t>1178</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8338</t>
+          <t>8270</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>54,85%</t>
+          <t>54,4%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>933</t>
+          <t>936</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7077</t>
+          <t>7189</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>46,56%</t>
+          <t>47,3%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3032</t>
+          <t>3065</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13205</t>
+          <t>12568</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>43,44%</t>
+          <t>41,34%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>10637</t>
+          <t>10462</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>21295</t>
+          <t>21165</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>40,32%</t>
+          <t>39,66%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>80,72%</t>
+          <t>80,23%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>17443</t>
+          <t>17816</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>29817</t>
+          <t>29969</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>47,96%</t>
+          <t>48,99%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>81,99%</t>
+          <t>82,4%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>33226</t>
+          <t>32660</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>48902</t>
+          <t>49164</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>52,95%</t>
+          <t>52,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>77,93%</t>
+          <t>78,35%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>930</t>
+          <t>909</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8192</t>
+          <t>7703</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>31,06%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1341,7 +1341,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4947</t>
+          <t>4978</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1356,7 +1356,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1009</t>
+          <t>1027</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>8723</t>
+          <t>9561</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>15,24%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6485</t>
+          <t>6767</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18337</t>
+          <t>18089</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>25,65%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>69,51%</t>
+          <t>68,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7413</t>
+          <t>7607</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18897</t>
+          <t>19162</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>51,96%</t>
+          <t>52,69%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>17190</t>
+          <t>16032</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>32835</t>
+          <t>32756</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>52,33%</t>
+          <t>52,2%</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6791</t>
+          <t>7196</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>27,28%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7825</t>
+          <t>7599</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>20861</t>
+          <t>20493</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>57,36%</t>
+          <t>56,35%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>9462</t>
+          <t>8797</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>23250</t>
+          <t>22755</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>37,05%</t>
+          <t>36,26%</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11531</t>
+          <t>11380</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>22837</t>
+          <t>22302</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>43,75%</t>
+          <t>43,18%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>86,65%</t>
+          <t>84,62%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>11005</t>
+          <t>10499</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>21677</t>
+          <t>20824</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>41,66%</t>
+          <t>39,74%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>82,05%</t>
+          <t>78,82%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>25902</t>
+          <t>26171</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>40865</t>
+          <t>41373</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>49,08%</t>
+          <t>49,59%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>77,43%</t>
+          <t>78,4%</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>948</t>
+          <t>938</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7533</t>
+          <t>7849</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>29,78%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>961</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7835</t>
+          <t>7686</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,65%</t>
+          <t>29,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3031</t>
+          <t>2950</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13969</t>
+          <t>13180</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>24,97%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4783</t>
+          <t>4840</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>15299</t>
+          <t>15310</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>58,05%</t>
+          <t>58,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>4114</t>
+          <t>4356</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>14405</t>
+          <t>14285</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>54,52%</t>
+          <t>54,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>11988</t>
+          <t>11499</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>25933</t>
+          <t>26882</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>49,14%</t>
+          <t>50,94%</t>
         </is>
       </c>
     </row>
@@ -1983,12 +1983,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1170</t>
+          <t>2089</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>12374</t>
+          <t>12562</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1998,12 +1998,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>46,95%</t>
+          <t>47,66%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4248</t>
+          <t>4111</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>14199</t>
+          <t>13962</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2033,12 +2033,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>53,74%</t>
+          <t>52,84%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2053,12 +2053,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7754</t>
+          <t>8269</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>22495</t>
+          <t>21964</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2068,12 +2068,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>42,63%</t>
+          <t>41,62%</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>17600</t>
+          <t>17091</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>30975</t>
+          <t>31062</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>42,48%</t>
+          <t>41,25%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>74,76%</t>
+          <t>74,97%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9404</t>
+          <t>9760</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>20679</t>
+          <t>20870</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>32,47%</t>
+          <t>33,7%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>71,4%</t>
+          <t>72,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>30753</t>
+          <t>30229</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>48550</t>
+          <t>48394</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>43,69%</t>
+          <t>42,94%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>68,97%</t>
+          <t>68,75%</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6128</t>
+          <t>6242</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>18673</t>
+          <t>18470</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>45,07%</t>
+          <t>44,58%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8367</t>
+          <t>6558</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>22,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>7104</t>
+          <t>7102</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>20600</t>
+          <t>22374</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>31,78%</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>7914</t>
+          <t>8200</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>20420</t>
+          <t>19382</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>49,29%</t>
+          <t>46,78%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4377</t>
+          <t>4181</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>15064</t>
+          <t>15104</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>52,01%</t>
+          <t>52,15%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>14509</t>
+          <t>15139</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>31099</t>
+          <t>31745</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>44,18%</t>
+          <t>45,1%</t>
         </is>
       </c>
     </row>
@@ -2439,12 +2439,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2097</t>
+          <t>2849</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11596</t>
+          <t>12486</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2454,12 +2454,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>30,14%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2474,12 +2474,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5910</t>
+          <t>6496</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>17285</t>
+          <t>17521</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2489,12 +2489,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>22,43%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>59,68%</t>
+          <t>60,5%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2509,12 +2509,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>11283</t>
+          <t>10855</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>26756</t>
+          <t>26461</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2524,12 +2524,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>38,01%</t>
+          <t>37,59%</t>
         </is>
       </c>
     </row>
@@ -2556,12 +2556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>57249</t>
+          <t>55486</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>77847</t>
+          <t>78290</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>52,35%</t>
+          <t>50,73%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>71,18%</t>
+          <t>71,59%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2591,12 +2591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>55232</t>
+          <t>55119</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>76516</t>
+          <t>76255</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2606,12 +2606,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>51,64%</t>
+          <t>51,54%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>71,54%</t>
+          <t>71,3%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>117916</t>
+          <t>117157</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>147087</t>
+          <t>147876</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>54,51%</t>
+          <t>54,16%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>68,0%</t>
+          <t>68,36%</t>
         </is>
       </c>
     </row>
@@ -2669,12 +2669,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>12226</t>
+          <t>12508</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>29752</t>
+          <t>30662</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2684,12 +2684,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>4125</t>
+          <t>4369</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>16680</t>
+          <t>16111</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2719,12 +2719,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>19817</t>
+          <t>19570</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>40649</t>
+          <t>42080</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>19,45%</t>
         </is>
       </c>
     </row>
@@ -2782,12 +2782,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>30546</t>
+          <t>31229</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>53643</t>
+          <t>52413</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2797,12 +2797,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>28,55%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>49,05%</t>
+          <t>47,92%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2817,12 +2817,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>24440</t>
+          <t>24308</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>45004</t>
+          <t>45114</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2832,12 +2832,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>42,08%</t>
+          <t>42,18%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>60545</t>
+          <t>60319</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>90964</t>
+          <t>89254</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>27,88%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>42,05%</t>
+          <t>41,26%</t>
         </is>
       </c>
     </row>
@@ -2895,12 +2895,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>10773</t>
+          <t>10363</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>27710</t>
+          <t>27833</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2910,12 +2910,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>28103</t>
+          <t>27274</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>50006</t>
+          <t>47331</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2945,12 +2945,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>46,76%</t>
+          <t>44,25%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>41755</t>
+          <t>42263</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>70122</t>
+          <t>69254</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2980,12 +2980,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>32,42%</t>
+          <t>32,02%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7393</t>
+          <t>7136</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18947</t>
+          <t>18620</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>61,34%</t>
+          <t>60,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>7924</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18702</t>
+          <t>18569</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>31,48%</t>
+          <t>31,0%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>73,16%</t>
+          <t>72,64%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>18653</t>
+          <t>18296</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>34258</t>
+          <t>34470</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>33,04%</t>
+          <t>32,41%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>60,68%</t>
+          <t>61,06%</t>
         </is>
       </c>
     </row>
@@ -3362,7 +3362,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>8360</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>27,06%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1018</t>
+          <t>1009</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8272</t>
+          <t>8701</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3407,12 +3407,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>32,36%</t>
+          <t>34,04%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1656</t>
+          <t>1601</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>11708</t>
+          <t>11604</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>20,56%</t>
         </is>
       </c>
     </row>
@@ -3470,12 +3470,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4134</t>
+          <t>4133</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14742</t>
+          <t>14488</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3490,7 +3490,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>47,73%</t>
+          <t>46,9%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3505,12 +3505,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2052</t>
+          <t>1943</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10475</t>
+          <t>10536</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3520,12 +3520,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>40,98%</t>
+          <t>41,22%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>7843</t>
+          <t>7897</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>21813</t>
+          <t>21515</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>38,64%</t>
+          <t>38,11%</t>
         </is>
       </c>
     </row>
@@ -3583,12 +3583,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6212</t>
+          <t>5454</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17892</t>
+          <t>17255</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3598,12 +3598,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>57,92%</t>
+          <t>55,86%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3618,12 +3618,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5036</t>
+          <t>5360</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15518</t>
+          <t>15898</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3633,12 +3633,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>60,71%</t>
+          <t>62,19%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3653,12 +3653,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>14189</t>
+          <t>13358</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>29426</t>
+          <t>28807</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3668,12 +3668,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>52,13%</t>
+          <t>51,03%</t>
         </is>
       </c>
     </row>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>17465</t>
+          <t>16874</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>29173</t>
+          <t>29047</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>44,21%</t>
+          <t>42,71%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>73,85%</t>
+          <t>73,53%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>10486</t>
+          <t>10393</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>23152</t>
+          <t>22988</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>31,14%</t>
+          <t>30,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>68,75%</t>
+          <t>68,26%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>30889</t>
+          <t>30669</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>48798</t>
+          <t>48723</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3785,12 +3785,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>42,21%</t>
+          <t>41,91%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>66,68%</t>
+          <t>66,58%</t>
         </is>
       </c>
     </row>
@@ -3813,12 +3813,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2730</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11858</t>
+          <t>10886</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3828,12 +3828,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>27,56%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3853,7 +3853,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6700</t>
+          <t>6369</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3868,7 +3868,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>3752</t>
+          <t>3847</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>14392</t>
+          <t>14908</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>20,37%</t>
         </is>
       </c>
     </row>
@@ -3926,12 +3926,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11601</t>
+          <t>11653</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23557</t>
+          <t>23747</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3941,12 +3941,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>29,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>59,63%</t>
+          <t>60,11%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6887</t>
+          <t>7014</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19065</t>
+          <t>20522</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3976,12 +3976,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>56,62%</t>
+          <t>60,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>22349</t>
+          <t>22394</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>39872</t>
+          <t>40388</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4011,12 +4011,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>30,54%</t>
+          <t>30,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>54,49%</t>
+          <t>55,19%</t>
         </is>
       </c>
     </row>
@@ -4044,7 +4044,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7237</t>
+          <t>7716</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4059,7 +4059,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4074,12 +4074,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2085</t>
+          <t>2112</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>12120</t>
+          <t>11501</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>35,99%</t>
+          <t>34,15%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4109,12 +4109,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4085</t>
+          <t>3945</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>15754</t>
+          <t>15973</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>21,83%</t>
         </is>
       </c>
     </row>
@@ -4156,12 +4156,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>12217</t>
+          <t>12299</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>23262</t>
+          <t>23539</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>39,68%</t>
+          <t>39,94%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>75,55%</t>
+          <t>76,45%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6471</t>
+          <t>5706</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>15605</t>
+          <t>15638</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>31,87%</t>
+          <t>28,11%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>76,87%</t>
+          <t>77,03%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>22057</t>
+          <t>21974</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>36240</t>
+          <t>36678</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4241,12 +4241,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>43,17%</t>
+          <t>43,01%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>70,93%</t>
+          <t>71,79%</t>
         </is>
       </c>
     </row>
@@ -4269,12 +4269,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>862</t>
+          <t>866</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7735</t>
+          <t>7956</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4309,7 +4309,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5628</t>
+          <t>5615</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4324,7 +4324,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>27,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1098</t>
+          <t>1094</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9170</t>
+          <t>9888</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>19,35%</t>
         </is>
       </c>
     </row>
@@ -4382,12 +4382,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2914</t>
+          <t>3096</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>12747</t>
+          <t>12952</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>41,4%</t>
+          <t>42,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2282</t>
+          <t>2138</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>11213</t>
+          <t>10516</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>55,23%</t>
+          <t>51,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>7385</t>
+          <t>7302</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>20124</t>
+          <t>20094</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>39,39%</t>
+          <t>39,33%</t>
         </is>
       </c>
     </row>
@@ -4495,12 +4495,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3201</t>
+          <t>3154</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>13162</t>
+          <t>13302</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4510,12 +4510,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>42,75%</t>
+          <t>43,2%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -4530,12 +4530,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>1024</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>7842</t>
+          <t>8011</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>38,63%</t>
+          <t>39,46%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -4565,12 +4565,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>5244</t>
+          <t>5510</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>17726</t>
+          <t>17895</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>34,69%</t>
+          <t>35,03%</t>
         </is>
       </c>
     </row>
@@ -4612,12 +4612,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>20443</t>
+          <t>20613</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>36255</t>
+          <t>36716</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>34,94%</t>
+          <t>35,23%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>61,97%</t>
+          <t>62,76%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4647,12 +4647,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>17534</t>
+          <t>16514</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>29856</t>
+          <t>29208</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>47,93%</t>
+          <t>45,14%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>81,6%</t>
+          <t>79,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4682,12 +4682,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>41582</t>
+          <t>42024</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>62377</t>
+          <t>62126</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>43,73%</t>
+          <t>44,19%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>65,6%</t>
+          <t>65,33%</t>
         </is>
       </c>
     </row>
@@ -4725,12 +4725,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2575</t>
+          <t>2660</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13155</t>
+          <t>13788</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4760,12 +4760,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>961</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8094</t>
+          <t>7584</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4795,12 +4795,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4985</t>
+          <t>4813</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>17343</t>
+          <t>17751</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>18,67%</t>
         </is>
       </c>
     </row>
@@ -4838,12 +4838,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>18007</t>
+          <t>18062</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>32390</t>
+          <t>33062</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4853,12 +4853,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>30,87%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>55,36%</t>
+          <t>56,51%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4873,12 +4873,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>8793</t>
+          <t>9014</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>21655</t>
+          <t>22207</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>59,19%</t>
+          <t>60,7%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4908,12 +4908,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>30642</t>
+          <t>30872</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>49897</t>
+          <t>50630</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>32,22%</t>
+          <t>32,47%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>52,47%</t>
+          <t>53,24%</t>
         </is>
       </c>
     </row>
@@ -4951,12 +4951,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9591</t>
+          <t>9085</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>24213</t>
+          <t>23281</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4966,12 +4966,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>41,39%</t>
+          <t>39,8%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5289</t>
+          <t>5736</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>17783</t>
+          <t>17413</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5001,12 +5001,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>48,6%</t>
+          <t>47,59%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5021,12 +5021,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>17918</t>
+          <t>18554</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>36937</t>
+          <t>36032</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>38,84%</t>
+          <t>37,89%</t>
         </is>
       </c>
     </row>
@@ -5068,12 +5068,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>69928</t>
+          <t>69918</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>95964</t>
+          <t>94738</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>43,79%</t>
+          <t>43,78%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>60,1%</t>
+          <t>59,33%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>52283</t>
+          <t>53034</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>76630</t>
+          <t>75580</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>45,02%</t>
+          <t>45,67%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>65,99%</t>
+          <t>65,08%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5138,12 +5138,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>131253</t>
+          <t>131008</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>165398</t>
+          <t>166096</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>47,59%</t>
+          <t>47,5%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>59,97%</t>
+          <t>60,22%</t>
         </is>
       </c>
     </row>
@@ -5181,12 +5181,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>10482</t>
+          <t>9844</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>26977</t>
+          <t>25970</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5196,12 +5196,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5216,12 +5216,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>4200</t>
+          <t>4458</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>15993</t>
+          <t>17587</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5251,12 +5251,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>17675</t>
+          <t>18302</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>38486</t>
+          <t>38607</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>14,0%</t>
         </is>
       </c>
     </row>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>47067</t>
+          <t>46341</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>71353</t>
+          <t>70995</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5309,12 +5309,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>29,02%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>44,68%</t>
+          <t>44,46%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5329,12 +5329,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>28939</t>
+          <t>29060</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>51378</t>
+          <t>50732</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5344,12 +5344,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>44,24%</t>
+          <t>43,69%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5364,12 +5364,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>80188</t>
+          <t>82236</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>113112</t>
+          <t>114733</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5379,12 +5379,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>29,82%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>41,01%</t>
+          <t>41,6%</t>
         </is>
       </c>
     </row>
@@ -5407,12 +5407,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>26384</t>
+          <t>26818</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>47921</t>
+          <t>48850</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5422,12 +5422,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>30,59%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>21031</t>
+          <t>21083</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>40709</t>
+          <t>41399</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5457,12 +5457,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>35,06%</t>
+          <t>35,65%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>52593</t>
+          <t>52459</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>82205</t>
+          <t>81742</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5492,12 +5492,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>29,64%</t>
         </is>
       </c>
     </row>
@@ -5751,32 +5751,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>40234</t>
+          <t>45883</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>32324</t>
+          <t>38072</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>48801</t>
+          <t>55392</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>43,78%</t>
+          <t>45,51%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>37,76%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>53,11%</t>
+          <t>54,94%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5786,32 +5786,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>39500</t>
+          <t>43306</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>33188</t>
+          <t>36900</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>46255</t>
+          <t>50757</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>40,51%</t>
+          <t>40,9%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>34,04%</t>
+          <t>34,85%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>47,44%</t>
+          <t>47,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5821,32 +5821,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>79734</t>
+          <t>89189</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>68782</t>
+          <t>78056</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>89735</t>
+          <t>100778</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>42,1%</t>
+          <t>43,14%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>36,32%</t>
+          <t>37,76%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>47,38%</t>
+          <t>48,75%</t>
         </is>
       </c>
     </row>
@@ -5864,32 +5864,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>59575</t>
+          <t>64191</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>51753</t>
+          <t>54235</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>66957</t>
+          <t>71913</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>64,83%</t>
+          <t>63,66%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>56,32%</t>
+          <t>53,79%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>72,87%</t>
+          <t>71,32%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5899,32 +5899,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>58263</t>
+          <t>63489</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>51534</t>
+          <t>55648</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>64418</t>
+          <t>69901</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>59,76%</t>
+          <t>59,96%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>52,86%</t>
+          <t>52,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>66,07%</t>
+          <t>66,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5934,32 +5934,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>117838</t>
+          <t>127681</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>107939</t>
+          <t>115814</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>128460</t>
+          <t>137787</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>62,22%</t>
+          <t>61,77%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>56,99%</t>
+          <t>56,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>67,83%</t>
+          <t>66,65%</t>
         </is>
       </c>
     </row>
@@ -5977,32 +5977,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5396</t>
+          <t>6203</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2319</t>
+          <t>2819</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10715</t>
+          <t>11880</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6012,32 +6012,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>9530</t>
+          <t>10692</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5808</t>
+          <t>6543</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>14130</t>
+          <t>15229</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6047,32 +6047,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>14926</t>
+          <t>16895</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>9960</t>
+          <t>10657</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>21830</t>
+          <t>24432</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,82%</t>
         </is>
       </c>
     </row>
@@ -6090,7 +6090,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>578</t>
+          <t>573</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -6100,12 +6100,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3043</t>
+          <t>3003</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -6115,7 +6115,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6125,7 +6125,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>369</t>
+          <t>375</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -6135,12 +6135,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2075</t>
+          <t>2124</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6160,7 +6160,7 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>947</t>
+          <t>948</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
@@ -6170,12 +6170,12 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3307</t>
+          <t>3603</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
@@ -6185,7 +6185,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,74%</t>
         </is>
       </c>
     </row>
@@ -6207,32 +6207,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>307392</t>
+          <t>70356</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>159533</t>
+          <t>60510</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>364084</t>
+          <t>81930</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>79,43%</t>
+          <t>45,69%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>41,23%</t>
+          <t>39,3%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>53,21%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6242,32 +6242,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>49519</t>
+          <t>54903</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>42507</t>
+          <t>46923</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>58241</t>
+          <t>64168</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>38,93%</t>
+          <t>39,12%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>33,42%</t>
+          <t>33,44%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>45,79%</t>
+          <t>45,73%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6277,32 +6277,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>356911</t>
+          <t>125259</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>208066</t>
+          <t>111846</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>457506</t>
+          <t>140405</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>69,42%</t>
+          <t>42,56%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>40,47%</t>
+          <t>38,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,98%</t>
+          <t>47,71%</t>
         </is>
       </c>
     </row>
@@ -6320,32 +6320,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>339415</t>
+          <t>100933</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>251674</t>
+          <t>90050</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>375139</t>
+          <t>111582</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>87,71%</t>
+          <t>65,55%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>65,04%</t>
+          <t>58,49%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>72,47%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6355,32 +6355,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>90508</t>
+          <t>99409</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>82874</t>
+          <t>90893</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>97268</t>
+          <t>106883</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>71,16%</t>
+          <t>70,84%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>65,16%</t>
+          <t>64,77%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>76,48%</t>
+          <t>76,16%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6390,32 +6390,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>429923</t>
+          <t>200342</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>345243</t>
+          <t>185053</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>486901</t>
+          <t>211961</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>83,62%</t>
+          <t>68,07%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>67,15%</t>
+          <t>62,88%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>72,02%</t>
         </is>
       </c>
     </row>
@@ -6433,32 +6433,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>263147</t>
+          <t>20670</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>43272</t>
+          <t>13680</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>353332</t>
+          <t>29457</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>68,0%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6468,22 +6468,22 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>16448</t>
+          <t>18242</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11379</t>
+          <t>12553</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23097</t>
+          <t>25612</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -6493,7 +6493,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6503,32 +6503,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>279594</t>
+          <t>38912</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>61145</t>
+          <t>29222</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>432740</t>
+          <t>50137</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>54,38%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>84,16%</t>
+          <t>17,04%</t>
         </is>
       </c>
     </row>
@@ -6546,67 +6546,67 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1768</t>
+          <t>1778</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
+          <t>503</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>4863</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>1,15%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0,33%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>3,16%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>432</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>7598</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>0,46%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>2194</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>0,31%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>1,96%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>2266</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>0,33%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6616,32 +6616,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>2182</t>
+          <t>2211</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>604</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>6229</t>
+          <t>5690</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,93%</t>
         </is>
       </c>
     </row>
@@ -6663,32 +6663,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>42661</t>
+          <t>49451</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>33704</t>
+          <t>39667</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>52191</t>
+          <t>59528</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>40,0%</t>
+          <t>41,88%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>33,6%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>48,93%</t>
+          <t>50,42%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6698,32 +6698,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>25713</t>
+          <t>30163</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>19851</t>
+          <t>23339</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>32231</t>
+          <t>36653</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>35,56%</t>
+          <t>35,45%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>44,58%</t>
+          <t>43,08%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6733,32 +6733,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>68374</t>
+          <t>79615</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>58053</t>
+          <t>68464</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>80487</t>
+          <t>92153</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>38,21%</t>
+          <t>39,19%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>32,44%</t>
+          <t>33,7%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>44,97%</t>
+          <t>45,36%</t>
         </is>
       </c>
     </row>
@@ -6776,32 +6776,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>65318</t>
+          <t>70019</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>55456</t>
+          <t>59414</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>74504</t>
+          <t>79426</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>61,24%</t>
+          <t>59,3%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>52,0%</t>
+          <t>50,32%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>69,86%</t>
+          <t>67,27%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6811,32 +6811,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>55952</t>
+          <t>64405</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>49997</t>
+          <t>58094</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>60808</t>
+          <t>70071</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>77,38%</t>
+          <t>75,69%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>69,15%</t>
+          <t>68,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>84,1%</t>
+          <t>82,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6846,32 +6846,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>121269</t>
+          <t>134424</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>110452</t>
+          <t>121880</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>131492</t>
+          <t>146368</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>67,76%</t>
+          <t>66,17%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>61,72%</t>
+          <t>59,99%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>73,48%</t>
+          <t>72,05%</t>
         </is>
       </c>
     </row>
@@ -6889,32 +6889,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>25615</t>
+          <t>27223</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>18049</t>
+          <t>19216</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>34662</t>
+          <t>37173</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>32,5%</t>
+          <t>31,48%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6924,32 +6924,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>11733</t>
+          <t>15164</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>7489</t>
+          <t>10285</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>17025</t>
+          <t>21438</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6959,22 +6959,22 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>37348</t>
+          <t>42387</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>28788</t>
+          <t>32688</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>47591</t>
+          <t>53311</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
@@ -6984,7 +6984,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>26,24%</t>
         </is>
       </c>
     </row>
@@ -7002,7 +7002,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>1124</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -7012,12 +7012,12 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5048</t>
+          <t>5556</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -7027,7 +7027,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -7037,7 +7037,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1347</t>
+          <t>1383</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4491</t>
+          <t>4290</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
@@ -7062,7 +7062,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -7072,32 +7072,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2370</t>
+          <t>2507</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>655</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7296</t>
+          <t>7218</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,55%</t>
         </is>
       </c>
     </row>
@@ -7119,32 +7119,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>80142</t>
+          <t>81713</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>66950</t>
+          <t>70530</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>90642</t>
+          <t>93541</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>41,91%</t>
+          <t>41,27%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>35,02%</t>
+          <t>35,62%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>47,41%</t>
+          <t>47,24%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7154,32 +7154,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>59571</t>
+          <t>63814</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>50636</t>
+          <t>53364</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>69606</t>
+          <t>74435</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>32,89%</t>
+          <t>32,4%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>27,09%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>38,43%</t>
+          <t>37,79%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7189,32 +7189,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>139713</t>
+          <t>145526</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>125489</t>
+          <t>129689</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>155358</t>
+          <t>159850</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>37,52%</t>
+          <t>36,85%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>33,7%</t>
+          <t>32,84%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>41,73%</t>
+          <t>40,47%</t>
         </is>
       </c>
     </row>
@@ -7232,32 +7232,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>124738</t>
+          <t>131099</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>113156</t>
+          <t>118646</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>135936</t>
+          <t>141981</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>65,24%</t>
+          <t>66,21%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>59,18%</t>
+          <t>59,92%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>71,1%</t>
+          <t>71,71%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7267,32 +7267,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>133284</t>
+          <t>145600</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>123944</t>
+          <t>134725</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>141895</t>
+          <t>154571</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>73,59%</t>
+          <t>73,92%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>68,43%</t>
+          <t>68,4%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>78,34%</t>
+          <t>78,48%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7302,32 +7302,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>258021</t>
+          <t>276698</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>243682</t>
+          <t>261772</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>272746</t>
+          <t>290827</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>69,3%</t>
+          <t>70,06%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>65,45%</t>
+          <t>66,28%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>73,26%</t>
+          <t>73,63%</t>
         </is>
       </c>
     </row>
@@ -7345,32 +7345,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>21810</t>
+          <t>22052</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>14820</t>
+          <t>14967</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>30572</t>
+          <t>31512</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7380,32 +7380,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>16213</t>
+          <t>17979</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>11601</t>
+          <t>12619</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>23136</t>
+          <t>25713</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7415,32 +7415,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>38024</t>
+          <t>40031</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>29513</t>
+          <t>30677</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>48725</t>
+          <t>50726</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>12,84%</t>
         </is>
       </c>
     </row>
@@ -7575,32 +7575,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>470429</t>
+          <t>247403</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>324645</t>
+          <t>224008</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>638546</t>
+          <t>268391</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>60,57%</t>
+          <t>43,34%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>41,8%</t>
+          <t>39,24%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>82,21%</t>
+          <t>47,01%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7610,32 +7610,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>174304</t>
+          <t>192185</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>159143</t>
+          <t>176466</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>189444</t>
+          <t>209550</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>36,38%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>33,29%</t>
+          <t>33,4%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>39,62%</t>
+          <t>39,67%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7645,32 +7645,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>644732</t>
+          <t>439588</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>488561</t>
+          <t>413953</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>939193</t>
+          <t>465238</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>51,38%</t>
+          <t>39,99%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>38,93%</t>
+          <t>37,66%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>74,85%</t>
+          <t>42,33%</t>
         </is>
       </c>
     </row>
@@ -7688,32 +7688,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>589045</t>
+          <t>366242</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>491588</t>
+          <t>344945</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>699871</t>
+          <t>388744</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>75,84%</t>
+          <t>64,15%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>63,29%</t>
+          <t>60,42%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>90,1%</t>
+          <t>68,1%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7723,32 +7723,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>338007</t>
+          <t>372902</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>323663</t>
+          <t>356019</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>351987</t>
+          <t>388187</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>70,7%</t>
+          <t>70,59%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>67,7%</t>
+          <t>67,39%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>73,62%</t>
+          <t>73,48%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7758,32 +7758,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>927052</t>
+          <t>739144</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>840970</t>
+          <t>713361</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1087759</t>
+          <t>763640</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>73,88%</t>
+          <t>67,25%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>67,02%</t>
+          <t>64,9%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>86,69%</t>
+          <t>69,48%</t>
         </is>
       </c>
     </row>
@@ -7801,32 +7801,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>315969</t>
+          <t>76147</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>96806</t>
+          <t>61756</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>574811</t>
+          <t>94022</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>40,68%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>74,0%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7836,32 +7836,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>53924</t>
+          <t>62077</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>44454</t>
+          <t>51114</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>64367</t>
+          <t>73872</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7871,32 +7871,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>369892</t>
+          <t>138224</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>148812</t>
+          <t>120008</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>786892</t>
+          <t>155990</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>62,71%</t>
+          <t>14,19%</t>
         </is>
       </c>
     </row>
@@ -7914,32 +7914,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3368</t>
+          <t>3475</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>1134</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>8265</t>
+          <t>8062</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7949,22 +7949,22 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>2131</t>
+          <t>2190</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>594</t>
+          <t>656</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>5537</t>
+          <t>5722</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
@@ -7974,7 +7974,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7984,32 +7984,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>5499</t>
+          <t>5665</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2137</t>
+          <t>2978</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>10686</t>
+          <t>12210</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>1,11%</t>
         </is>
       </c>
     </row>
